--- a/public/datos/2.2_BUSCARV_consolidado.xlsx
+++ b/public/datos/2.2_BUSCARV_consolidado.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Documentos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Procesos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Responsables" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Consolidado" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Enunciado_Caso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Documentos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Procesos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Responsables" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Consolidado_Auditoria" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,6 +429,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Detalle del Requerimiento / Parámetros del Caso</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Código de Actividad</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Título del Caso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Consolidación relacional de auditoría con blindaje de errores</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Organización</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lácteos del Caribe S.A.S. - Sistema Integrado de Gestión</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. Situación Problema</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>La información del SIG está fragmentada en 3 hojas independientes: inventario de documentos (códigos), catálogo de procesos y directorio de responsables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2. Misión del Aprendiz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Construir la hoja Consolidado_Auditoria cruzando las fuentes con BUSCARV o BUSCARX, envolviendo con SI.ERROR para reemplazar errores #N/D por 'SIN ASIGNAR'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Requerimiento 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cruce de Proceso: Extraer Nombre del Proceso y Macroproceso (Tipo) desde la hoja Procesos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Requerimiento 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cruce de Responsable: Traer Nombre del Responsable y Correo Corporativo desde la hoja Responsables cruzando el ID responsable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Requerimiento 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tratamiento de Excepciones: El proceso PA-03 Mantenimiento no tiene responsable asignado y generará #N/D. Envolver con =SI.ERROR(BUSCARV(...); 'SIN ASIGNAR').</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dificultad Clave / Regla Técnica</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>En BUSCARV el código buscado debe estar en la columna 1 del rango y el 4to argumento debe ser coincidencia exacta (FALSO o 0). Todo el cruce de líderes debe protegerse con SI.ERROR.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1138,7 +1277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1396,7 +1535,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1614,25 +1753,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Código documento</t>
+          <t>Código Documento</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1642,12 +1784,27 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Proceso</t>
+          <t>Código Proceso</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Responsable</t>
+          <t>Nombre del Proceso</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Macroproceso (Tipo)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Responsable Líder</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Correo Corporativo</t>
         </is>
       </c>
     </row>
@@ -1662,6 +1819,11 @@
           <t>Política del SIG</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PE-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1674,6 +1836,11 @@
           <t>Plan estratégico 2025-2028</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PE-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1686,6 +1853,11 @@
           <t>Revisión por la dirección</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PE-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1698,6 +1870,11 @@
           <t>Acta de revisión por la dirección</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PE-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1710,6 +1887,11 @@
           <t>Manual del SIG</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PE-02</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1722,6 +1904,11 @@
           <t>Control de documentos</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PE-02</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1734,6 +1921,11 @@
           <t>Auditorías internas</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PE-02</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1746,6 +1938,11 @@
           <t>Acciones correctivas</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PE-02</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1758,6 +1955,11 @@
           <t>Listado maestro de documentos</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PE-02</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1770,6 +1972,11 @@
           <t>Plan de auditoría</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PE-02</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1782,6 +1989,11 @@
           <t>Control de producción</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PM-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1794,6 +2006,11 @@
           <t>Limpieza y desinfección de equipos</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PM-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1806,6 +2023,11 @@
           <t>Pasteurización</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PM-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1818,6 +2040,11 @@
           <t>Registro de temperatura</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PM-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1830,6 +2057,11 @@
           <t>Control de lotes</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PM-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1842,6 +2074,11 @@
           <t>Producto no conforme</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PM-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1854,6 +2091,11 @@
           <t>Atención de PQRS</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PM-02</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1866,6 +2108,11 @@
           <t>Ventas y cotizaciones</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PM-02</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1878,6 +2125,11 @@
           <t>Encuesta de satisfacción</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PM-02</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1890,6 +2142,11 @@
           <t>Registro de PQRS</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PM-02</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1902,6 +2159,11 @@
           <t>Despacho y entrega</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PM-03</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1914,6 +2176,11 @@
           <t>Cargue de vehículos</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PM-03</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1926,6 +2193,11 @@
           <t>Lista de chequeo de vehículos</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PM-03</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1938,6 +2210,11 @@
           <t>Control de inventario</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PM-03</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1950,6 +2227,11 @@
           <t>Selección y contratación</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PA-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1962,6 +2244,11 @@
           <t>Inducción y reinducción</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PA-01</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1974,6 +2261,11 @@
           <t>Evaluación de desempeño</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PA-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1986,6 +2278,11 @@
           <t>Plan de capacitación 2026</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PA-01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1998,6 +2295,11 @@
           <t>Compras y evaluación de proveedores</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PA-02</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2010,6 +2312,11 @@
           <t>Orden de compra</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PA-02</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2022,6 +2329,11 @@
           <t>Evaluación de proveedores</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PA-02</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2034,6 +2346,11 @@
           <t>Mantenimiento preventivo</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PA-03</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2046,6 +2363,11 @@
           <t>Hoja de vida de equipos</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PA-03</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2058,6 +2380,11 @@
           <t>Solicitud de mantenimiento</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PA-03</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2070,6 +2397,11 @@
           <t>Plan de emergencias</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PA-04</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2082,6 +2414,11 @@
           <t>Reporte de incidentes y accidentes</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PA-04</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2094,6 +2431,11 @@
           <t>Manual de SST</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PA-04</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2106,6 +2448,11 @@
           <t>Inspección de EPP</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PA-04</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2118,6 +2465,11 @@
           <t>Trabajo en alturas</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PA-04</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2128,6 +2480,11 @@
       <c r="B41" t="inlineStr">
         <is>
           <t>Matriz de peligros</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PA-04</t>
         </is>
       </c>
     </row>
